--- a/アプリケーション企画実習/DB/テーブル詳細一覧.xlsx
+++ b/アプリケーション企画実習/DB/テーブル詳細一覧.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.10.253\Studio1\企画制作実習_2026_05\B_久曜上野小橋タイガース\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.10.253\Studio1\企画制作実習_2026_05\B_久曜上野小橋タイガース\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCE2040-9C85-47D0-ADB2-A1C1330AE009}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB282FC-5B02-40F9-A25E-A4EFF4177B79}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="11895" xr2:uid="{ACCA7A6E-E5CB-4EDE-B27B-2B20B6E310F2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12015" xr2:uid="{ACCA7A6E-E5CB-4EDE-B27B-2B20B6E310F2}"/>
   </bookViews>
   <sheets>
     <sheet name="猫" sheetId="11" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">犬!$A$2:$O$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">団体!$A$2:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">猫!$A$2:$N$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">里親!$A$2:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">里親!$A$2:$H$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="753">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -3039,10 +3039,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>イベント種別(eventshubetsu)テーブル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>モコ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3700,9 +3696,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>犬の写真柴犬まで</t>
-  </si>
-  <si>
     <t>譲渡済</t>
     <rPh sb="0" eb="3">
       <t>ジョウトズミ</t>
@@ -3808,6 +3801,10 @@
     <rPh sb="0" eb="4">
       <t>セイネンガッピ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イベント種別(event_type)テーブル</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3960,7 +3957,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3984,19 +3981,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -4043,24 +4027,6 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -4075,6 +4041,66 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4402,7 +4428,7 @@
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.125" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.125" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="70.75" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="56.625" bestFit="1" customWidth="1"/>
   </cols>
@@ -4425,7 +4451,7 @@
       <c r="D2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="18" t="s">
         <v>86</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -4446,14 +4472,14 @@
       <c r="K2" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="12" t="s">
         <v>90</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>435</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -4469,10 +4495,10 @@
       <c r="D3" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="8">
         <v>46033</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="27" t="s">
         <v>227</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -4481,7 +4507,7 @@
       <c r="H3" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="8">
         <v>45816</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -4490,7 +4516,7 @@
       <c r="K3" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="13">
         <v>392144829103756</v>
       </c>
       <c r="M3" s="2" t="s">
@@ -4513,10 +4539,10 @@
       <c r="D4" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="9">
         <v>45962</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -4525,7 +4551,7 @@
       <c r="H4" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="9">
         <v>45502</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -4534,7 +4560,7 @@
       <c r="K4" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="14">
         <v>392149103847265</v>
       </c>
       <c r="M4" s="3"/>
@@ -4553,19 +4579,19 @@
       <c r="D5" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="9">
         <v>46231</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="26" t="s">
         <v>230</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I5" s="14">
+        <v>746</v>
+      </c>
+      <c r="I5" s="9">
         <v>45325</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -4574,7 +4600,7 @@
       <c r="K5" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="14">
         <v>392142564910387</v>
       </c>
       <c r="M5" s="3"/>
@@ -4593,10 +4619,10 @@
       <c r="D6" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="9">
         <v>46366</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="26" t="s">
         <v>226</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -4605,7 +4631,7 @@
       <c r="H6" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="9">
         <v>45977</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -4614,7 +4640,7 @@
       <c r="K6" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="14">
         <v>392147382019465</v>
       </c>
       <c r="M6" s="3" t="s">
@@ -4635,10 +4661,10 @@
       <c r="D7" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="9">
         <v>46097</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="26" t="s">
         <v>229</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -4647,7 +4673,7 @@
       <c r="H7" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="9">
         <v>45110</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -4656,7 +4682,7 @@
       <c r="K7" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="14">
         <v>392141902837465</v>
       </c>
       <c r="M7" s="3" t="s">
@@ -4677,11 +4703,11 @@
       <c r="D8" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="9">
         <v>45799</v>
       </c>
-      <c r="F8" s="37" t="s">
-        <v>746</v>
+      <c r="F8" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>421</v>
@@ -4689,7 +4715,7 @@
       <c r="H8" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="9">
         <v>44952</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -4698,7 +4724,7 @@
       <c r="K8" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="14">
         <v>392146482019387</v>
       </c>
       <c r="M8" s="3"/>
@@ -4719,19 +4745,19 @@
       <c r="D9" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="9">
         <v>45653</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="26" t="s">
         <v>227</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I9" s="14">
+        <v>743</v>
+      </c>
+      <c r="I9" s="9">
         <v>45143</v>
       </c>
       <c r="J9" s="3" t="s">
@@ -4740,7 +4766,7 @@
       <c r="K9" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="14">
         <v>392143029184756</v>
       </c>
       <c r="M9" s="3"/>
@@ -4759,10 +4785,10 @@
       <c r="D10" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="9">
         <v>45969</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -4771,7 +4797,7 @@
       <c r="H10" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="9">
         <v>45689</v>
       </c>
       <c r="J10" s="3" t="s">
@@ -4780,7 +4806,7 @@
       <c r="K10" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="14">
         <v>392148592013476</v>
       </c>
       <c r="M10" s="3" t="s">
@@ -4801,10 +4827,10 @@
       <c r="D11" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="9">
         <v>45108</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="26" t="s">
         <v>422</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -4813,7 +4839,7 @@
       <c r="H11" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="9">
         <v>44945</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -4822,7 +4848,7 @@
       <c r="K11" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="14">
         <v>392145142039876</v>
       </c>
       <c r="M11" s="3"/>
@@ -4843,10 +4869,10 @@
       <c r="D12" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="9">
         <v>46275</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="26" t="s">
         <v>226</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -4855,7 +4881,7 @@
       <c r="H12" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="9">
         <v>46040</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -4864,12 +4890,12 @@
       <c r="K12" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="14">
         <v>392149203847165</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
@@ -4885,19 +4911,19 @@
       <c r="D13" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="9">
         <v>46007</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>421</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I13" s="14">
+        <v>746</v>
+      </c>
+      <c r="I13" s="9">
         <v>45392</v>
       </c>
       <c r="J13" s="3" t="s">
@@ -4906,7 +4932,7 @@
       <c r="K13" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="14">
         <v>392142384910276</v>
       </c>
       <c r="M13" s="3"/>
@@ -4927,10 +4953,10 @@
       <c r="D14" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="9">
         <v>46256</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="26" t="s">
         <v>227</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -4939,7 +4965,7 @@
       <c r="H14" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="9">
         <v>45438</v>
       </c>
       <c r="J14" s="3" t="s">
@@ -4948,7 +4974,7 @@
       <c r="K14" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="14">
         <v>392147102938465</v>
       </c>
       <c r="M14" s="3"/>
@@ -4969,19 +4995,19 @@
       <c r="D15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="9">
         <v>46075</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="26" t="s">
         <v>228</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I15" s="14">
+        <v>746</v>
+      </c>
+      <c r="I15" s="9">
         <v>45753</v>
       </c>
       <c r="J15" s="3" t="s">
@@ -4990,7 +5016,7 @@
       <c r="K15" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="14">
         <v>392141829304765</v>
       </c>
       <c r="M15" s="3"/>
@@ -5009,19 +5035,19 @@
       <c r="D16" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="9">
         <v>46113</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="26" t="s">
         <v>428</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>223</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I16" s="14">
+        <v>743</v>
+      </c>
+      <c r="I16" s="9">
         <v>45315</v>
       </c>
       <c r="J16" s="3" t="s">
@@ -5030,7 +5056,7 @@
       <c r="K16" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="14">
         <v>392146392018475</v>
       </c>
       <c r="M16" s="3"/>
@@ -5049,10 +5075,10 @@
       <c r="D17" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="9">
         <v>46281</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="26" t="s">
         <v>227</v>
       </c>
       <c r="G17" s="3" t="s">
@@ -5061,7 +5087,7 @@
       <c r="H17" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="9">
         <v>46055</v>
       </c>
       <c r="J17" s="3" t="s">
@@ -5070,7 +5096,7 @@
       <c r="K17" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="14">
         <v>392143492018576</v>
       </c>
       <c r="M17" s="3" t="s">
@@ -5093,19 +5119,19 @@
       <c r="D18" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="9">
         <v>46161</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="26" t="s">
         <v>229</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>224</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I18" s="14">
+        <v>743</v>
+      </c>
+      <c r="I18" s="9">
         <v>45666</v>
       </c>
       <c r="J18" s="3" t="s">
@@ -5114,7 +5140,7 @@
       <c r="K18" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="14">
         <v>392148102938476</v>
       </c>
       <c r="M18" s="3"/>
@@ -5133,10 +5159,10 @@
       <c r="D19" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="9">
         <v>46145</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="26" t="s">
         <v>226</v>
       </c>
       <c r="G19" s="3" t="s">
@@ -5145,7 +5171,7 @@
       <c r="H19" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="9">
         <v>45757</v>
       </c>
       <c r="J19" s="3" t="s">
@@ -5154,7 +5180,7 @@
       <c r="K19" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="14">
         <v>392145920138476</v>
       </c>
       <c r="M19" s="3"/>
@@ -5175,11 +5201,11 @@
       <c r="D20" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="9">
         <v>46282</v>
       </c>
-      <c r="F20" s="37" t="s">
-        <v>746</v>
+      <c r="F20" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>421</v>
@@ -5187,7 +5213,7 @@
       <c r="H20" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="9">
         <v>46159</v>
       </c>
       <c r="J20" s="3" t="s">
@@ -5196,7 +5222,7 @@
       <c r="K20" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="14">
         <v>392142103948756</v>
       </c>
       <c r="M20" s="3"/>
@@ -5217,10 +5243,10 @@
       <c r="D21" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="9">
         <v>45677</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -5229,7 +5255,7 @@
       <c r="H21" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="9">
         <v>44946</v>
       </c>
       <c r="J21" s="3" t="s">
@@ -5238,7 +5264,7 @@
       <c r="K21" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="14">
         <v>392147920134876</v>
       </c>
       <c r="M21" s="3"/>
@@ -5257,10 +5283,10 @@
       <c r="D22" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="9">
         <v>46098</v>
       </c>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="26" t="s">
         <v>428</v>
       </c>
       <c r="G22" s="3" t="s">
@@ -5269,7 +5295,7 @@
       <c r="H22" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="9">
         <v>45733</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -5278,12 +5304,12 @@
       <c r="K22" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="14">
         <v>392141392048756</v>
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.4">
@@ -5299,19 +5325,19 @@
       <c r="D23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="9">
         <v>46143</v>
       </c>
-      <c r="F23" s="37" t="s">
-        <v>746</v>
+      <c r="F23" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>421</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I23" s="14">
+        <v>746</v>
+      </c>
+      <c r="I23" s="9">
         <v>46012</v>
       </c>
       <c r="J23" s="3" t="s">
@@ -5320,7 +5346,7 @@
       <c r="K23" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="14">
         <v>392146201938475</v>
       </c>
       <c r="M23" s="3"/>
@@ -5341,19 +5367,19 @@
       <c r="D24" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="9">
         <v>46131</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="26" t="s">
         <v>230</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I24" s="14">
+        <v>746</v>
+      </c>
+      <c r="I24" s="9">
         <v>45035</v>
       </c>
       <c r="J24" s="3" t="s">
@@ -5362,7 +5388,7 @@
       <c r="K24" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="14">
         <v>392143820194756</v>
       </c>
       <c r="M24" s="3"/>
@@ -5381,10 +5407,10 @@
       <c r="D25" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="9">
         <v>46152</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="26" t="s">
         <v>424</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -5393,7 +5419,7 @@
       <c r="H25" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="9">
         <v>45787</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -5402,12 +5428,12 @@
       <c r="K25" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="14">
         <v>392148492013876</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.4">
@@ -5423,19 +5449,19 @@
       <c r="D26" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="9">
         <v>45668</v>
       </c>
-      <c r="F26" s="37" t="s">
-        <v>746</v>
+      <c r="F26" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>421</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I26" s="14">
+        <v>743</v>
+      </c>
+      <c r="I26" s="9">
         <v>45413</v>
       </c>
       <c r="J26" s="3" t="s">
@@ -5444,7 +5470,7 @@
       <c r="K26" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="14">
         <v>392145029183746</v>
       </c>
       <c r="M26" s="3"/>
@@ -5465,19 +5491,19 @@
       <c r="D27" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="9">
         <v>46065</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="26" t="s">
         <v>227</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I27" s="14">
+        <v>743</v>
+      </c>
+      <c r="I27" s="9">
         <v>45220</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -5486,7 +5512,7 @@
       <c r="K27" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="14">
         <v>392149382014756</v>
       </c>
       <c r="M27" s="3"/>
@@ -5505,11 +5531,11 @@
       <c r="D28" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="9">
         <v>46282</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>746</v>
+      <c r="F28" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>421</v>
@@ -5517,7 +5543,7 @@
       <c r="H28" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="9">
         <v>46109</v>
       </c>
       <c r="J28" s="3" t="s">
@@ -5526,7 +5552,7 @@
       <c r="K28" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="14">
         <v>392142710394856</v>
       </c>
       <c r="M28" s="3"/>
@@ -5547,10 +5573,10 @@
       <c r="D29" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="9">
         <v>45831</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="26" t="s">
         <v>230</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -5559,7 +5585,7 @@
       <c r="H29" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="9">
         <v>44930</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -5568,7 +5594,7 @@
       <c r="K29" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="14">
         <v>392147492013856</v>
       </c>
       <c r="M29" s="3"/>
@@ -5589,19 +5615,19 @@
       <c r="D30" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="9">
         <v>45310</v>
       </c>
-      <c r="F30" s="37" t="s">
+      <c r="F30" s="26" t="s">
         <v>427</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I30" s="14">
+        <v>743</v>
+      </c>
+      <c r="I30" s="9">
         <v>44945</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -5610,7 +5636,7 @@
       <c r="K30" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="14">
         <v>392141203948765</v>
       </c>
       <c r="M30" s="3"/>
@@ -5629,11 +5655,11 @@
       <c r="D31" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="9">
         <v>46282</v>
       </c>
-      <c r="F31" s="37" t="s">
-        <v>746</v>
+      <c r="F31" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>421</v>
@@ -5641,7 +5667,7 @@
       <c r="H31" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="9">
         <v>46050</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -5650,7 +5676,7 @@
       <c r="K31" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="14">
         <v>392146920138456</v>
       </c>
       <c r="M31" s="3"/>
@@ -5671,10 +5697,10 @@
       <c r="D32" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="9">
         <v>46150</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="26" t="s">
         <v>428</v>
       </c>
       <c r="G32" s="3" t="s">
@@ -5683,7 +5709,7 @@
       <c r="H32" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="9">
         <v>45785</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -5692,7 +5718,7 @@
       <c r="K32" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="14">
         <v>392143102948756</v>
       </c>
       <c r="M32" s="3"/>
@@ -5711,19 +5737,19 @@
       <c r="D33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="9">
         <v>46020</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I33" s="14">
+        <v>746</v>
+      </c>
+      <c r="I33" s="9">
         <v>45289</v>
       </c>
       <c r="J33" s="3" t="s">
@@ -5732,7 +5758,7 @@
       <c r="K33" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="14">
         <v>392148029138476</v>
       </c>
       <c r="M33" s="3"/>
@@ -5751,10 +5777,10 @@
       <c r="D34" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="9">
         <v>46283</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F34" s="26" t="s">
         <v>229</v>
       </c>
       <c r="G34" s="3" t="s">
@@ -5763,7 +5789,7 @@
       <c r="H34" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I34" s="14">
+      <c r="I34" s="9">
         <v>46040</v>
       </c>
       <c r="J34" s="3" t="s">
@@ -5772,7 +5798,7 @@
       <c r="K34" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="14">
         <v>392145392014876</v>
       </c>
       <c r="M34" s="3"/>
@@ -5791,19 +5817,19 @@
       <c r="D35" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="9">
         <v>46062</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="26" t="s">
         <v>428</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>223</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I35" s="14">
+        <v>746</v>
+      </c>
+      <c r="I35" s="9">
         <v>45697</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -5812,7 +5838,7 @@
       <c r="K35" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="14">
         <v>392149492013876</v>
       </c>
       <c r="M35" s="3"/>
@@ -5831,19 +5857,19 @@
       <c r="D36" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="9">
         <v>45983</v>
       </c>
-      <c r="F36" s="37" t="s">
+      <c r="F36" s="26" t="s">
         <v>226</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>222</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I36" s="14">
+        <v>743</v>
+      </c>
+      <c r="I36" s="9">
         <v>45252</v>
       </c>
       <c r="J36" s="3" t="s">
@@ -5852,7 +5878,7 @@
       <c r="K36" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="14">
         <v>392142019384765</v>
       </c>
       <c r="M36" s="3"/>
@@ -5871,10 +5897,10 @@
       <c r="D37" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="9">
         <v>46223</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G37" s="3" t="s">
@@ -5883,7 +5909,7 @@
       <c r="H37" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="9">
         <v>45493</v>
       </c>
       <c r="J37" s="3" t="s">
@@ -5892,7 +5918,7 @@
       <c r="K37" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="14">
         <v>392147592013876</v>
       </c>
       <c r="M37" s="3"/>
@@ -5911,19 +5937,19 @@
       <c r="D38" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="9">
         <v>46081</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="26" t="s">
         <v>428</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I38" s="14">
+        <v>743</v>
+      </c>
+      <c r="I38" s="9">
         <v>45716</v>
       </c>
       <c r="J38" s="3" t="s">
@@ -5932,7 +5958,7 @@
       <c r="K38" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L38" s="19">
+      <c r="L38" s="14">
         <v>392141592038476</v>
       </c>
       <c r="M38" s="3"/>
@@ -5951,19 +5977,19 @@
       <c r="D39" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="9">
         <v>45920</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="26" t="s">
         <v>427</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I39" s="14">
+        <v>743</v>
+      </c>
+      <c r="I39" s="9">
         <v>45555</v>
       </c>
       <c r="J39" s="3" t="s">
@@ -5972,7 +5998,7 @@
       <c r="K39" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="14">
         <v>392146029138476</v>
       </c>
       <c r="M39" s="3"/>
@@ -5991,11 +6017,11 @@
       <c r="D40" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="9">
         <v>46162</v>
       </c>
-      <c r="F40" s="37" t="s">
-        <v>746</v>
+      <c r="F40" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>421</v>
@@ -6003,7 +6029,7 @@
       <c r="H40" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="9">
         <v>45798</v>
       </c>
       <c r="J40" s="3" t="s">
@@ -6012,7 +6038,7 @@
       <c r="K40" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="14">
         <v>392143592014876</v>
       </c>
       <c r="M40" s="3"/>
@@ -6033,10 +6059,10 @@
       <c r="D41" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="9">
         <v>46270</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="26" t="s">
         <v>426</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -6045,7 +6071,7 @@
       <c r="H41" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="9">
         <v>45540</v>
       </c>
       <c r="J41" s="3" t="s">
@@ -6054,7 +6080,7 @@
       <c r="K41" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="14">
         <v>392148201938476</v>
       </c>
       <c r="M41" s="3" t="s">
@@ -6075,10 +6101,10 @@
       <c r="D42" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="9">
         <v>45837</v>
       </c>
-      <c r="F42" s="37" t="s">
+      <c r="F42" s="26" t="s">
         <v>424</v>
       </c>
       <c r="G42" s="3" t="s">
@@ -6087,7 +6113,7 @@
       <c r="H42" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I42" s="9">
         <v>45106</v>
       </c>
       <c r="J42" s="3" t="s">
@@ -6096,7 +6122,7 @@
       <c r="K42" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="14">
         <v>392145792013876</v>
       </c>
       <c r="M42" s="3"/>
@@ -6115,19 +6141,19 @@
       <c r="D43" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="9">
         <v>46117</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>223</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="I43" s="14">
+        <v>746</v>
+      </c>
+      <c r="I43" s="9">
         <v>45752</v>
       </c>
       <c r="J43" s="3" t="s">
@@ -6136,7 +6162,7 @@
       <c r="K43" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="14">
         <v>392149192038476</v>
       </c>
       <c r="M43" s="3"/>
@@ -6155,19 +6181,19 @@
       <c r="D44" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="9">
         <v>46115</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F44" s="26" t="s">
         <v>422</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>421</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I44" s="14">
+        <v>743</v>
+      </c>
+      <c r="I44" s="9">
         <v>45683</v>
       </c>
       <c r="J44" s="3" t="s">
@@ -6176,12 +6202,12 @@
       <c r="K44" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="14">
         <v>392142492013876</v>
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.4">
@@ -6197,19 +6223,19 @@
       <c r="D45" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="9">
         <v>45738</v>
       </c>
-      <c r="F45" s="37" t="s">
+      <c r="F45" s="26" t="s">
         <v>227</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I45" s="14">
+        <v>743</v>
+      </c>
+      <c r="I45" s="9">
         <v>45007</v>
       </c>
       <c r="J45" s="3" t="s">
@@ -6218,7 +6244,7 @@
       <c r="K45" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="14">
         <v>392147029138476</v>
       </c>
       <c r="M45" s="3"/>
@@ -6237,11 +6263,11 @@
       <c r="D46" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="9">
         <v>45744</v>
       </c>
-      <c r="F46" s="37" t="s">
-        <v>746</v>
+      <c r="F46" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>421</v>
@@ -6249,7 +6275,7 @@
       <c r="H46" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I46" s="14">
+      <c r="I46" s="9">
         <v>45335</v>
       </c>
       <c r="J46" s="3" t="s">
@@ -6258,7 +6284,7 @@
       <c r="K46" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="14">
         <v>392141792038476</v>
       </c>
       <c r="M46" s="3"/>
@@ -6279,19 +6305,19 @@
       <c r="D47" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E47" s="15">
+      <c r="E47" s="10">
         <v>45830</v>
       </c>
-      <c r="F47" s="36" t="s">
+      <c r="F47" s="25" t="s">
         <v>228</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>222</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>745</v>
-      </c>
-      <c r="I47" s="15">
+        <v>743</v>
+      </c>
+      <c r="I47" s="10">
         <v>45099</v>
       </c>
       <c r="J47" s="4" t="s">
@@ -6300,7 +6326,7 @@
       <c r="K47" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="L47" s="20">
+      <c r="L47" s="15">
         <v>392146820193876</v>
       </c>
       <c r="M47" s="4"/>
@@ -6330,7 +6356,7 @@
     <col min="10" max="10" width="9.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.125" style="16" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="97.75" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="85.875" bestFit="1" customWidth="1"/>
   </cols>
@@ -6339,9 +6365,6 @@
       <c r="A1" t="s">
         <v>196</v>
       </c>
-      <c r="D1" t="s">
-        <v>744</v>
-      </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
@@ -6369,7 +6392,7 @@
         <v>233</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>436</v>
@@ -6380,14 +6403,14 @@
       <c r="L2" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="17" t="s">
         <v>90</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>451</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.4">
@@ -6403,19 +6426,19 @@
       <c r="D3" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="8">
         <v>45762</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="27" t="s">
         <v>460</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>225</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="I3" s="13">
+        <v>743</v>
+      </c>
+      <c r="I3" s="8">
         <v>45397</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -6427,7 +6450,7 @@
       <c r="L3" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="19">
         <v>392144102938476</v>
       </c>
       <c r="N3" s="2"/>
@@ -6446,10 +6469,10 @@
       <c r="D4" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="9">
         <v>46105</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="26" t="s">
         <v>228</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -6458,7 +6481,7 @@
       <c r="H4" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="9">
         <v>45740</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -6470,7 +6493,7 @@
       <c r="L4" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="20">
         <v>392149820134876</v>
       </c>
       <c r="N4" s="3"/>
@@ -6491,11 +6514,11 @@
       <c r="D5" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="9">
         <v>46027</v>
       </c>
-      <c r="F5" s="37" t="s">
-        <v>746</v>
+      <c r="F5" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>461</v>
@@ -6503,7 +6526,7 @@
       <c r="H5" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="9">
         <v>45794</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -6515,7 +6538,7 @@
       <c r="L5" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M5" s="25">
+      <c r="M5" s="20">
         <v>392142392014876</v>
       </c>
       <c r="N5" s="3"/>
@@ -6534,19 +6557,19 @@
       <c r="D6" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="9">
         <v>46027</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="26" t="s">
         <v>457</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>462</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I6" s="14">
+        <v>743</v>
+      </c>
+      <c r="I6" s="9">
         <v>45955</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -6558,7 +6581,7 @@
       <c r="L6" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="20">
         <v>392147201938476</v>
       </c>
       <c r="N6" s="3"/>
@@ -6577,19 +6600,19 @@
       <c r="D7" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="9">
         <v>46284</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="26" t="s">
         <v>463</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>462</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I7" s="14">
+        <v>743</v>
+      </c>
+      <c r="I7" s="9">
         <v>45919</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -6601,7 +6624,7 @@
       <c r="L7" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="20">
         <v>392141492013876</v>
       </c>
       <c r="N7" s="3"/>
@@ -6622,19 +6645,19 @@
       <c r="D8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="9">
         <v>45705</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I8" s="14">
+        <v>743</v>
+      </c>
+      <c r="I8" s="9">
         <v>45124</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -6646,7 +6669,7 @@
       <c r="L8" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="20">
         <v>392146102938476</v>
       </c>
       <c r="N8" s="3"/>
@@ -6667,19 +6690,19 @@
       <c r="D9" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="9">
         <v>46113</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="26" t="s">
         <v>458</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I9" s="14">
+        <v>743</v>
+      </c>
+      <c r="I9" s="9">
         <v>45392</v>
       </c>
       <c r="J9" s="3" t="s">
@@ -6691,7 +6714,7 @@
       <c r="L9" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="20">
         <v>392143201938476</v>
       </c>
       <c r="N9" s="3"/>
@@ -6710,19 +6733,19 @@
       <c r="D10" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="9">
         <v>45571</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="26" t="s">
         <v>228</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I10" s="14">
+        <v>743</v>
+      </c>
+      <c r="I10" s="9">
         <v>44475</v>
       </c>
       <c r="J10" s="3" t="s">
@@ -6734,7 +6757,7 @@
       <c r="L10" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="20">
         <v>392148392014876</v>
       </c>
       <c r="N10" s="3" t="s">
@@ -6755,19 +6778,19 @@
       <c r="D11" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="9">
         <v>46033</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="26" t="s">
         <v>227</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>224</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I11" s="14">
+        <v>743</v>
+      </c>
+      <c r="I11" s="9">
         <v>45376</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -6779,7 +6802,7 @@
       <c r="L11" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="20">
         <v>392145492013876</v>
       </c>
       <c r="N11" s="3" t="s">
@@ -6800,19 +6823,19 @@
       <c r="D12" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="9">
         <v>45747</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I12" s="14">
+        <v>743</v>
+      </c>
+      <c r="I12" s="9">
         <v>44568</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -6824,7 +6847,7 @@
       <c r="L12" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="20">
         <v>392149592013876</v>
       </c>
       <c r="N12" s="3"/>
@@ -6845,11 +6868,11 @@
       <c r="D13" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="9">
         <v>46047</v>
       </c>
-      <c r="F13" s="37" t="s">
-        <v>746</v>
+      <c r="F13" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>461</v>
@@ -6857,7 +6880,7 @@
       <c r="H13" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="9">
         <v>45347</v>
       </c>
       <c r="J13" s="3" t="s">
@@ -6869,7 +6892,7 @@
       <c r="L13" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="20">
         <v>392142820193876</v>
       </c>
       <c r="N13" s="3"/>
@@ -6890,19 +6913,19 @@
       <c r="D14" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="9">
         <v>46292</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I14" s="14">
+        <v>743</v>
+      </c>
+      <c r="I14" s="9">
         <v>46161</v>
       </c>
       <c r="J14" s="3" t="s">
@@ -6914,7 +6937,7 @@
       <c r="L14" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="20">
         <v>392147820193876</v>
       </c>
       <c r="N14" s="3"/>
@@ -6935,19 +6958,19 @@
       <c r="D15" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="9">
         <v>45849</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>465</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I15" s="14">
+        <v>743</v>
+      </c>
+      <c r="I15" s="9">
         <v>45057</v>
       </c>
       <c r="J15" s="3" t="s">
@@ -6959,7 +6982,7 @@
       <c r="L15" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="20">
         <v>392141102938476</v>
       </c>
       <c r="N15" s="3" t="s">
@@ -6979,22 +7002,22 @@
       <c r="C16" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="9">
         <v>45016</v>
       </c>
-      <c r="F16" s="37" t="s">
-        <v>746</v>
+      <c r="F16" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I16" s="14">
+        <v>743</v>
+      </c>
+      <c r="I16" s="9">
         <v>44677</v>
       </c>
       <c r="J16" s="3" t="s">
@@ -7006,7 +7029,7 @@
       <c r="L16" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="20">
         <v>392146792013876</v>
       </c>
       <c r="N16" s="3"/>
@@ -7027,19 +7050,19 @@
       <c r="D17" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="9">
         <v>45340</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="26" t="s">
         <v>458</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I17" s="14">
+        <v>743</v>
+      </c>
+      <c r="I17" s="9">
         <v>44975</v>
       </c>
       <c r="J17" s="3" t="s">
@@ -7051,7 +7074,7 @@
       <c r="L17" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="20">
         <v>392143920138476</v>
       </c>
       <c r="N17" s="3" t="s">
@@ -7072,19 +7095,19 @@
       <c r="D18" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="9">
         <v>46112</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I18" s="14">
+        <v>743</v>
+      </c>
+      <c r="I18" s="9">
         <v>45200</v>
       </c>
       <c r="J18" s="3" t="s">
@@ -7096,7 +7119,7 @@
       <c r="L18" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M18" s="25">
+      <c r="M18" s="20">
         <v>392148792013876</v>
       </c>
       <c r="N18" s="3"/>
@@ -7117,19 +7140,19 @@
       <c r="D19" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="9">
         <v>45016</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I19" s="14">
+        <v>743</v>
+      </c>
+      <c r="I19" s="9">
         <v>44561</v>
       </c>
       <c r="J19" s="3" t="s">
@@ -7141,7 +7164,7 @@
       <c r="L19" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="20">
         <v>392145201938476</v>
       </c>
       <c r="N19" s="3"/>
@@ -7162,19 +7185,19 @@
       <c r="D20" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="9">
         <v>46071</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I20" s="14">
+        <v>743</v>
+      </c>
+      <c r="I20" s="9">
         <v>45706</v>
       </c>
       <c r="J20" s="3" t="s">
@@ -7186,7 +7209,7 @@
       <c r="L20" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="20">
         <v>392142920138476</v>
       </c>
       <c r="N20" s="3"/>
@@ -7205,10 +7228,10 @@
       <c r="D21" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="9">
         <v>46112</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="26" t="s">
         <v>458</v>
       </c>
       <c r="G21" s="3" t="s">
@@ -7217,7 +7240,7 @@
       <c r="H21" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="9">
         <v>44890</v>
       </c>
       <c r="J21" s="3" t="s">
@@ -7229,7 +7252,7 @@
       <c r="L21" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M21" s="25">
+      <c r="M21" s="20">
         <v>392147692013876</v>
       </c>
       <c r="N21" s="3"/>
@@ -7248,19 +7271,19 @@
       <c r="D22" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="9">
         <v>45601</v>
       </c>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="26" t="s">
         <v>227</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I22" s="14">
+        <v>743</v>
+      </c>
+      <c r="I22" s="9">
         <v>44870</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -7272,7 +7295,7 @@
       <c r="L22" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M22" s="25">
+      <c r="M22" s="20">
         <v>392141692013876</v>
       </c>
       <c r="N22" s="3"/>
@@ -7291,10 +7314,10 @@
       <c r="D23" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="9">
         <v>46056</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="F23" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -7303,7 +7326,7 @@
       <c r="H23" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="9">
         <v>45594</v>
       </c>
       <c r="J23" s="3" t="s">
@@ -7315,7 +7338,7 @@
       <c r="L23" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M23" s="25">
+      <c r="M23" s="20">
         <v>392146320193876</v>
       </c>
       <c r="N23" s="3"/>
@@ -7334,10 +7357,10 @@
       <c r="D24" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="9">
         <v>46197</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -7346,7 +7369,7 @@
       <c r="H24" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="9">
         <v>45180</v>
       </c>
       <c r="J24" s="3" t="s">
@@ -7358,7 +7381,7 @@
       <c r="L24" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="20">
         <v>392143792013876</v>
       </c>
       <c r="N24" s="3"/>
@@ -7379,10 +7402,10 @@
       <c r="D25" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="9">
         <v>46259</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="26" t="s">
         <v>474</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -7391,7 +7414,7 @@
       <c r="H25" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="9">
         <v>45529</v>
       </c>
       <c r="J25" s="3" t="s">
@@ -7403,7 +7426,7 @@
       <c r="L25" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M25" s="25">
+      <c r="M25" s="20">
         <v>392148692013876</v>
       </c>
       <c r="N25" s="3" t="s">
@@ -7426,19 +7449,19 @@
       <c r="D26" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="9">
         <v>46290</v>
       </c>
-      <c r="F26" s="37" t="s">
-        <v>746</v>
+      <c r="F26" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I26" s="14">
+        <v>743</v>
+      </c>
+      <c r="I26" s="9">
         <v>45554</v>
       </c>
       <c r="J26" s="3" t="s">
@@ -7450,7 +7473,7 @@
       <c r="L26" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M26" s="25">
+      <c r="M26" s="20">
         <v>392145692013876</v>
       </c>
       <c r="N26" s="3"/>
@@ -7469,19 +7492,19 @@
       <c r="D27" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="9">
         <v>46126</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I27" s="14">
+        <v>743</v>
+      </c>
+      <c r="I27" s="9">
         <v>45761</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -7493,7 +7516,7 @@
       <c r="L27" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M27" s="25">
+      <c r="M27" s="20">
         <v>392149692013876</v>
       </c>
       <c r="N27" s="3"/>
@@ -7512,19 +7535,19 @@
       <c r="D28" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="9">
         <v>45371</v>
       </c>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="26" t="s">
         <v>463</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>224</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I28" s="14">
+        <v>743</v>
+      </c>
+      <c r="I28" s="9">
         <v>44811</v>
       </c>
       <c r="J28" s="3" t="s">
@@ -7536,7 +7559,7 @@
       <c r="L28" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M28" s="25">
+      <c r="M28" s="20">
         <v>392142692013876</v>
       </c>
       <c r="N28" s="3" t="s">
@@ -7559,10 +7582,10 @@
       <c r="D29" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="9">
         <v>45935</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G29" s="3" t="s">
@@ -7571,7 +7594,7 @@
       <c r="H29" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="9">
         <v>45243</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -7583,7 +7606,7 @@
       <c r="L29" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M29" s="25">
+      <c r="M29" s="20">
         <v>392147320193876</v>
       </c>
       <c r="N29" s="3"/>
@@ -7604,19 +7627,19 @@
       <c r="D30" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="9">
         <v>46204</v>
       </c>
-      <c r="F30" s="37" t="s">
+      <c r="F30" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I30" s="14">
+        <v>743</v>
+      </c>
+      <c r="I30" s="9">
         <v>45969</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -7628,7 +7651,7 @@
       <c r="L30" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M30" s="25">
+      <c r="M30" s="20">
         <v>392141292013876</v>
       </c>
       <c r="N30" s="3"/>
@@ -7649,10 +7672,10 @@
       <c r="D31" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="9">
         <v>46266</v>
       </c>
-      <c r="F31" s="37" t="s">
+      <c r="F31" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -7661,7 +7684,7 @@
       <c r="H31" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="9">
         <v>46025</v>
       </c>
       <c r="J31" s="3" t="s">
@@ -7673,7 +7696,7 @@
       <c r="L31" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M31" s="25">
+      <c r="M31" s="20">
         <v>392146592013876</v>
       </c>
       <c r="N31" s="3"/>
@@ -7694,19 +7717,19 @@
       <c r="D32" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="9">
         <v>45377</v>
       </c>
-      <c r="F32" s="37" t="s">
-        <v>746</v>
+      <c r="F32" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I32" s="14">
+        <v>743</v>
+      </c>
+      <c r="I32" s="9">
         <v>44817</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -7718,7 +7741,7 @@
       <c r="L32" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M32" s="25">
+      <c r="M32" s="20">
         <v>392143320193876</v>
       </c>
       <c r="N32" s="3"/>
@@ -7739,10 +7762,10 @@
       <c r="D33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="9">
         <v>45791</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="26" t="s">
         <v>427</v>
       </c>
       <c r="G33" s="3" t="s">
@@ -7751,7 +7774,7 @@
       <c r="H33" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="9">
         <v>44905</v>
       </c>
       <c r="J33" s="3" t="s">
@@ -7763,7 +7786,7 @@
       <c r="L33" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M33" s="25">
+      <c r="M33" s="20">
         <v>392148920138476</v>
       </c>
       <c r="N33" s="3"/>
@@ -7782,19 +7805,19 @@
       <c r="D34" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="9">
         <v>46112</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F34" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I34" s="14">
+        <v>743</v>
+      </c>
+      <c r="I34" s="9">
         <v>45514</v>
       </c>
       <c r="J34" s="3" t="s">
@@ -7806,7 +7829,7 @@
       <c r="L34" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="20">
         <v>392145820193876</v>
       </c>
       <c r="N34" s="3"/>
@@ -7827,19 +7850,19 @@
       <c r="D35" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="9">
         <v>45350</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="26" t="s">
         <v>226</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I35" s="14">
+        <v>743</v>
+      </c>
+      <c r="I35" s="9">
         <v>44585</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -7851,7 +7874,7 @@
       <c r="L35" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M35" s="25">
+      <c r="M35" s="20">
         <v>392149920138476</v>
       </c>
       <c r="N35" s="3"/>
@@ -7870,19 +7893,19 @@
       <c r="D36" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="9">
         <v>46281</v>
       </c>
-      <c r="F36" s="37" t="s">
-        <v>746</v>
+      <c r="F36" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I36" s="14">
+        <v>743</v>
+      </c>
+      <c r="I36" s="9">
         <v>45873</v>
       </c>
       <c r="J36" s="3" t="s">
@@ -7894,12 +7917,12 @@
       <c r="L36" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M36" s="25">
+      <c r="M36" s="20">
         <v>392142201938476</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.4">
@@ -7915,10 +7938,10 @@
       <c r="D37" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="9">
         <v>45747</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G37" s="3" t="s">
@@ -7927,7 +7950,7 @@
       <c r="H37" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="9">
         <v>44914</v>
       </c>
       <c r="J37" s="3" t="s">
@@ -7939,7 +7962,7 @@
       <c r="L37" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M37" s="25">
+      <c r="M37" s="20">
         <v>392147792013876</v>
       </c>
       <c r="N37" s="3"/>
@@ -7960,19 +7983,19 @@
       <c r="D38" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="9">
         <v>45941</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="26" t="s">
         <v>423</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>225</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I38" s="14">
+        <v>743</v>
+      </c>
+      <c r="I38" s="9">
         <v>44511</v>
       </c>
       <c r="J38" s="3" t="s">
@@ -7984,7 +8007,7 @@
       <c r="L38" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M38" s="25">
+      <c r="M38" s="20">
         <v>392141092013876</v>
       </c>
       <c r="N38" s="3"/>
@@ -8003,19 +8026,19 @@
       <c r="D39" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="9">
         <v>45143</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="I39" s="14">
+        <v>743</v>
+      </c>
+      <c r="I39" s="9">
         <v>43983</v>
       </c>
       <c r="J39" s="3" t="s">
@@ -8027,7 +8050,7 @@
       <c r="L39" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M39" s="25">
+      <c r="M39" s="20">
         <v>392146692013876</v>
       </c>
       <c r="N39" s="3"/>
@@ -8048,11 +8071,11 @@
       <c r="D40" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="9">
         <v>46266</v>
       </c>
-      <c r="F40" s="37" t="s">
-        <v>746</v>
+      <c r="F40" s="26" t="s">
+        <v>744</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>461</v>
@@ -8060,7 +8083,7 @@
       <c r="H40" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="9">
         <v>43308</v>
       </c>
       <c r="J40" s="3" t="s">
@@ -8072,7 +8095,7 @@
       <c r="L40" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M40" s="25">
+      <c r="M40" s="20">
         <v>392143692013876</v>
       </c>
       <c r="N40" s="3" t="s">
@@ -8095,10 +8118,10 @@
       <c r="D41" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="9">
         <v>44494</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="26" t="s">
         <v>459</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -8107,7 +8130,7 @@
       <c r="H41" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="9">
         <v>43789</v>
       </c>
       <c r="J41" s="3" t="s">
@@ -8119,7 +8142,7 @@
       <c r="L41" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="M41" s="25">
+      <c r="M41" s="20">
         <v>392148820193876</v>
       </c>
       <c r="N41" s="3" t="s">
@@ -8142,11 +8165,11 @@
       <c r="D42" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="10">
         <v>46113</v>
       </c>
-      <c r="F42" s="36" t="s">
-        <v>746</v>
+      <c r="F42" s="25" t="s">
+        <v>744</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>461</v>
@@ -8154,7 +8177,7 @@
       <c r="H42" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="10">
         <v>43254</v>
       </c>
       <c r="J42" s="4" t="s">
@@ -8166,7 +8189,7 @@
       <c r="L42" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="M42" s="27">
+      <c r="M42" s="22">
         <v>392145592013876</v>
       </c>
       <c r="N42" s="4" t="s">
@@ -8208,7 +8231,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>84</v>
@@ -8230,787 +8253,787 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="28" t="s">
+        <v>578</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>608</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>640</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B4" s="29" t="s">
         <v>609</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C4" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="D4" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>641</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G4" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="29" t="s">
+        <v>580</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>610</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>638</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>642</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>643</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="29" t="s">
+        <v>582</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>612</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>644</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>613</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>645</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="29" t="s">
+        <v>584</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>614</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>639</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>646</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="29" t="s">
+        <v>585</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>615</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>647</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="29" t="s">
+        <v>586</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>616</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>648</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="C4" s="8" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="29" t="s">
+        <v>587</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="D12" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>649</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="29" t="s">
+        <v>588</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>618</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>650</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="29" t="s">
+        <v>589</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>651</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>590</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>620</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>652</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="29" t="s">
+        <v>591</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>621</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>653</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="29" t="s">
+        <v>592</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>622</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>654</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="29" t="s">
+        <v>593</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>623</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>655</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="29" t="s">
+        <v>594</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>624</v>
+      </c>
+      <c r="C19" s="29" t="s">
         <v>639</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="D19" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>656</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="29" t="s">
+        <v>595</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>625</v>
+      </c>
+      <c r="C20" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="H6" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
-        <v>583</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="D20" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" s="29" t="s">
+        <v>596</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>626</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>658</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" s="29" t="s">
+        <v>597</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>627</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>659</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>598</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>628</v>
+      </c>
+      <c r="C23" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
-        <v>584</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="D23" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>660</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="29" t="s">
+        <v>599</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>629</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>639</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>661</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" s="29" t="s">
+        <v>600</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>630</v>
+      </c>
+      <c r="C25" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H8" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="D25" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>662</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" s="29" t="s">
+        <v>601</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>631</v>
+      </c>
+      <c r="C26" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
-        <v>587</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="D26" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>663</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" s="29" t="s">
+        <v>602</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>632</v>
+      </c>
+      <c r="C27" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="H11" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="D27" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>664</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>633</v>
+      </c>
+      <c r="C28" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="H12" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="D28" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>665</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="29" t="s">
+        <v>604</v>
+      </c>
+      <c r="B29" s="29" t="s">
+        <v>634</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>638</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>666</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" s="29" t="s">
+        <v>605</v>
+      </c>
+      <c r="B30" s="29" t="s">
+        <v>635</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="F30" s="29" t="s">
+        <v>667</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="29" t="s">
+        <v>606</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>636</v>
+      </c>
+      <c r="C31" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H13" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="D31" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>668</v>
+      </c>
+      <c r="G31" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="C32" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="H15" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>622</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>655</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H17" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>624</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H18" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
-        <v>595</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H19" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>658</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="H21" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A22" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A23" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>640</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="H24" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H25" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" s="8" t="s">
-        <v>602</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="H26" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H27" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A28" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H28" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A29" s="8" t="s">
-        <v>605</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H29" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A30" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>668</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="H30" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A31" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" s="8" t="s">
+      <c r="D32" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" s="30" t="s">
         <v>669</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="G32" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A32" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="H32" t="s">
-        <v>700</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:F32" xr:uid="{1FFA1914-56AE-4CB2-AD77-546672346ED2}"/>
+  <autoFilter ref="A2:H2" xr:uid="{55C875EE-0FA4-4F25-B6E7-87F319479598}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9034,17 +9057,17 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>577</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+        <v>576</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -9074,757 +9097,757 @@
       <c r="I2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J2" s="34"/>
+      <c r="J2" s="23"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="31" t="s">
         <v>554</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="31" t="s">
         <v>440</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="32">
         <v>46332</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="33">
         <v>0.54166666666666663</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="31" t="s">
         <v>541</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="31">
         <v>4000</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="31" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="34" t="s">
         <v>554</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="34" t="s">
         <v>553</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="35">
         <v>46306</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="36">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="34" t="s">
         <v>513</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="34">
         <v>3000</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="34" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="34" t="s">
         <v>516</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="34" t="s">
         <v>526</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="35">
         <v>46282</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="36">
         <v>0.375</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="34" t="s">
         <v>525</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="34" t="s">
         <v>513</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="34">
         <v>25000</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="34" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="34" t="s">
         <v>550</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="35">
         <v>46291</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="36">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="34" t="s">
         <v>514</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="34" t="s">
         <v>513</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="34">
         <v>20000</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="34" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D7" s="35">
+        <v>46293</v>
+      </c>
+      <c r="E7" s="36">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="H7" s="37">
+        <v>22000</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D8" s="9">
+        <v>46314</v>
+      </c>
+      <c r="E8" s="36">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>524</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="37" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D9" s="35">
+        <v>46286</v>
+      </c>
+      <c r="E9" s="36">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="H9" s="37">
+        <v>5000</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A10" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D10" s="35">
+        <v>46284</v>
+      </c>
+      <c r="E10" s="36">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="H10" s="37">
+        <v>5000</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>566</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" s="35">
+        <v>46309</v>
+      </c>
+      <c r="E11" s="36">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>524</v>
+      </c>
+      <c r="H11" s="37"/>
+      <c r="I11" s="34" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="12" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D12" s="35">
+        <v>46277</v>
+      </c>
+      <c r="E12" s="36">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="H12" s="34">
+        <v>8000</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D13" s="35">
+        <v>46267</v>
+      </c>
+      <c r="E13" s="36">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>739</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="34" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" s="34" t="s">
+        <v>533</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D14" s="35">
+        <v>46287</v>
+      </c>
+      <c r="E14" s="36">
+        <v>0.625</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>739</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="34" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>539</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="D15" s="35">
+        <v>46334</v>
+      </c>
+      <c r="E15" s="36">
+        <v>0.4375</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>740</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>524</v>
+      </c>
+      <c r="H15" s="37"/>
+      <c r="I15" s="34" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>568</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="D16" s="35">
+        <v>46327</v>
+      </c>
+      <c r="E16" s="36">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="34" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A17" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D17" s="35">
+        <v>46366</v>
+      </c>
+      <c r="E17" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>524</v>
+      </c>
+      <c r="H17" s="34">
+        <v>4500</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>570</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D18" s="35">
+        <v>46295</v>
+      </c>
+      <c r="E18" s="36">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>524</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="34" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>534</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="D19" s="39">
+        <v>46351</v>
+      </c>
+      <c r="E19" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>739</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>524</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="34" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" s="34" t="s">
+        <v>533</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D20" s="35">
+        <v>46328</v>
+      </c>
+      <c r="E20" s="36">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>739</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="34" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D21" s="35">
+        <v>46327</v>
+      </c>
+      <c r="E21" s="36">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>740</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="34" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D22" s="35">
+        <v>46287</v>
+      </c>
+      <c r="E22" s="36">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="34" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D23" s="35">
+        <v>46330</v>
+      </c>
+      <c r="E23" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="H23" s="34">
+        <v>24000</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>526</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="D24" s="35">
+        <v>46295</v>
+      </c>
+      <c r="E24" s="36">
+        <v>0.625</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="34" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="37" t="s">
+        <v>522</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="35">
+        <v>46288</v>
+      </c>
+      <c r="E25" s="36">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>521</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="34" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="34" t="s">
         <v>516</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B26" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D26" s="35">
+        <v>46284</v>
+      </c>
+      <c r="E26" s="36">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="H26" s="34">
+        <v>100000</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="C27" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="D7" s="29">
-        <v>46293</v>
-      </c>
-      <c r="E7" s="28">
+      <c r="D27" s="35">
+        <v>46270</v>
+      </c>
+      <c r="E27" s="36">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="H27" s="34">
+        <v>220000</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="D28" s="35">
+        <v>46334</v>
+      </c>
+      <c r="E28" s="36">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="F28" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="40" t="s">
+        <v>554</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>442</v>
+      </c>
+      <c r="D29" s="41">
+        <v>46306</v>
+      </c>
+      <c r="E29" s="42">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>514</v>
+      </c>
+      <c r="G29" s="40" t="s">
         <v>513</v>
       </c>
-      <c r="H7" s="30">
-        <v>22000</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>519</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D8" s="33">
-        <v>46314</v>
-      </c>
-      <c r="E8" s="28">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="30" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>545</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D9" s="29">
-        <v>46286</v>
-      </c>
-      <c r="E9" s="28">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="H9" s="30">
-        <v>5000</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>544</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D10" s="29">
-        <v>46284</v>
-      </c>
-      <c r="E10" s="28">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="H10" s="30">
-        <v>5000</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D11" s="29">
-        <v>46309</v>
-      </c>
-      <c r="E11" s="28">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="G11" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="H11" s="30"/>
-      <c r="I11" s="12" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A12" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D12" s="29">
-        <v>46277</v>
-      </c>
-      <c r="E12" s="28">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>541</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="H12" s="12">
-        <v>8000</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D13" s="29">
-        <v>46267</v>
-      </c>
-      <c r="E13" s="28">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="12" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" s="12" t="s">
-        <v>533</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D14" s="29">
-        <v>46287</v>
-      </c>
-      <c r="E14" s="28">
-        <v>0.625</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="G14" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="12" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="12" t="s">
-        <v>531</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>539</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="D15" s="29">
-        <v>46334</v>
-      </c>
-      <c r="E15" s="28">
-        <v>0.4375</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>741</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="12" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="D16" s="29">
-        <v>46327</v>
-      </c>
-      <c r="E16" s="28">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="12" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A17" s="12" t="s">
-        <v>537</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D17" s="29">
-        <v>46366</v>
-      </c>
-      <c r="E17" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="H17" s="12">
-        <v>4500</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D18" s="29">
-        <v>46295</v>
-      </c>
-      <c r="E18" s="28">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="12" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="12" t="s">
-        <v>535</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>534</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>440</v>
-      </c>
-      <c r="D19" s="31">
-        <v>46351</v>
-      </c>
-      <c r="E19" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="G19" s="30" t="s">
-        <v>524</v>
-      </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="12" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="12" t="s">
-        <v>533</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D20" s="29">
-        <v>46328</v>
-      </c>
-      <c r="E20" s="28">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="12" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="12" t="s">
-        <v>531</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D21" s="29">
-        <v>46327</v>
-      </c>
-      <c r="E21" s="28">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>741</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="12" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D22" s="29">
-        <v>46287</v>
-      </c>
-      <c r="E22" s="28">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="12" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="12" t="s">
-        <v>528</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D23" s="29">
-        <v>46330</v>
-      </c>
-      <c r="E23" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H23" s="12">
-        <v>24000</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D24" s="29">
-        <v>46295</v>
-      </c>
-      <c r="E24" s="28">
-        <v>0.625</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="30" t="s">
-        <v>522</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="29">
-        <v>46288</v>
-      </c>
-      <c r="E25" s="28">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="12" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>519</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D26" s="29">
-        <v>46284</v>
-      </c>
-      <c r="E26" s="28">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="G26" s="30" t="s">
-        <v>513</v>
-      </c>
-      <c r="H26" s="12">
-        <v>100000</v>
-      </c>
-      <c r="I26" s="30" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>515</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D27" s="29">
-        <v>46270</v>
-      </c>
-      <c r="E27" s="28">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="H27" s="12">
-        <v>220000</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>574</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D28" s="29">
-        <v>46334</v>
-      </c>
-      <c r="E28" s="28">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="B29" s="12" t="s">
+      <c r="H29" s="40">
+        <v>7000</v>
+      </c>
+      <c r="I29" s="40" t="s">
         <v>575</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>442</v>
-      </c>
-      <c r="D29" s="29">
-        <v>46306</v>
-      </c>
-      <c r="E29" s="28">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="H29" s="12">
-        <v>7000</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -9845,7 +9868,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>566</v>
+        <v>752</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
@@ -9854,67 +9877,67 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="43" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="37" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="34" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="34" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="34" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="34" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="34" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="34" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="34" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="34" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="34" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="34" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="40" t="s">
         <v>522</v>
       </c>
     </row>
@@ -9970,233 +9993,233 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="2">
         <v>50</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="F4" s="3">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="F4" s="9">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="F6" s="3">
         <v>40</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F5" s="9">
+      <c r="G6" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="F7" s="3">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="F8" s="3">
         <v>30</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="G8" s="3" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" s="3">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="3">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="F11" s="3">
         <v>40</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="G11" s="3" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F12" s="4">
         <v>50</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="F8" s="9">
-        <v>30</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="F9" s="9">
-        <v>30</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="9">
-        <v>50</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="F11" s="9">
-        <v>40</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="G12" s="4" t="s">
         <v>709</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F12" s="9">
-        <v>50</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>710</v>
       </c>
     </row>
   </sheetData>
@@ -10222,7 +10245,7 @@
     <col min="8" max="8" width="28.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="52.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.4">
@@ -10266,703 +10289,703 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="44" t="s">
         <v>292</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="44" t="s">
         <v>492</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="44" t="s">
         <v>295</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="44" t="s">
         <v>296</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="45" t="s">
         <v>297</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="45" t="s">
         <v>298</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="45" t="s">
         <v>299</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A4" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>510</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>305</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>306</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A4" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>510</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A5" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>493</v>
+      </c>
+      <c r="C5" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="K4" s="9" t="s">
+      <c r="D5" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I5" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="J5" s="47" t="s">
+        <v>315</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="C5" s="10" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A6" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>321</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>322</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A7" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>495</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="I7" s="47" t="s">
+        <v>328</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>329</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A8" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>511</v>
+      </c>
+      <c r="C8" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="H5" s="11" t="s">
+      <c r="D8" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>332</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="H8" s="47" t="s">
         <v>313</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A6" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="I8" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A9" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>496</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>338</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>339</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>340</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>341</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>342</v>
+      </c>
+      <c r="J9" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A10" s="46" t="s">
+        <v>344</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>345</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I10" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J10" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A11" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>498</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>350</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>353</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I11" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J11" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A12" s="46" t="s">
+        <v>354</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>499</v>
+      </c>
+      <c r="C12" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="D12" s="46" t="s">
+        <v>355</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J12" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A13" s="46" t="s">
+        <v>359</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>364</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>365</v>
+      </c>
+      <c r="J13" s="47" t="s">
+        <v>366</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A14" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A15" s="46" t="s">
+        <v>372</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>502</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>375</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>376</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I15" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J15" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A16" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>503</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>378</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>380</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>382</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>383</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>384</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A17" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>504</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="G17" s="46" t="s">
+        <v>389</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J17" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A18" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>505</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>393</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>394</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J18" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A19" s="46" t="s">
+        <v>395</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>506</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>396</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>398</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>399</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I19" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J19" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A20" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>507</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>401</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>402</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>403</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>404</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="J20" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A21" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>508</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>406</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>407</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="G21" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>411</v>
+      </c>
+      <c r="J21" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="K21" s="34" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A22" s="48" t="s">
+        <v>413</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>509</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>414</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>415</v>
+      </c>
+      <c r="F22" s="48" t="s">
+        <v>416</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>417</v>
+      </c>
+      <c r="H22" s="49" t="s">
         <v>297</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A7" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A8" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A9" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A10" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A11" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A13" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A14" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A15" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A21" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="K21" s="12" t="s">
+      <c r="I22" s="49" t="s">
+        <v>418</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>419</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>729</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A22" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>509</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>419</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>730</v>
       </c>
     </row>
   </sheetData>
